--- a/Dario Kulici LB2 BewertungsrasterV25_26.xlsx
+++ b/Dario Kulici LB2 BewertungsrasterV25_26.xlsx
@@ -295,15 +295,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -311,15 +311,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -574,7 +574,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.9140625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.73"/>
@@ -604,12 +604,12 @@
         <v>2</v>
       </c>
       <c r="H1" s="3" t="n">
-        <f aca="false">E1/(COUNTA(D4:D14,F4:F14,H4:H14))*5+1</f>
-        <v>3.72727272727273</v>
+        <f aca="false">E1/(COUNTA(D4:D12,F4:F12,H4:H12))*5+1</f>
+        <v>4.33333333333333</v>
       </c>
       <c r="I1" s="1" t="n">
         <f aca="false">ROUND(H1,1.1)</f>
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Dario Kulici LB2 BewertungsrasterV25_26.xlsx
+++ b/Dario Kulici LB2 BewertungsrasterV25_26.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="35">
   <si>
     <t xml:space="preserve">Schüler</t>
   </si>
@@ -598,18 +598,18 @@
       </c>
       <c r="E1" s="3" t="n">
         <f aca="false">COUNTIF(C4:G14,"x")</f>
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="3" t="n">
         <f aca="false">E1/(COUNTA(D4:D12,F4:F12,H4:H12))*5+1</f>
-        <v>4.33333333333333</v>
+        <v>4.88888888888889</v>
       </c>
       <c r="I1" s="1" t="n">
         <f aca="false">ROUND(H1,1.1)</f>
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -891,15 +891,21 @@
       <c r="B14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="D14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="F14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="6"/>
+      <c r="G14" s="6" t="s">
+        <v>11</v>
+      </c>
       <c r="H14" s="6" t="s">
         <v>14</v>
       </c>
